--- a/x13dico_AS_master.xlsx
+++ b/x13dico_AS_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YWYD5I\Documents\00_RJD3_Developpement\RJD3_development\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40BCBF0-1AEC-4AED-AE91-2540CA0CE71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B63CCF0-F68B-4F1E-BC58-59A4B8F8F11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
